--- a/internal_master_rules.xlsx
+++ b/internal_master_rules.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kiran.maddoju_puresp\pyenv\IAG Supplier\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{606A890C-D62D-45E1-918B-324175CC408C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9929B2-FC4D-4221-91F7-B8F9B7A5A376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C9D5D7F3-0C06-4E4F-B852-8461133596F0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="18">
   <si>
     <t>France</t>
   </si>
@@ -122,7 +122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -145,15 +145,47 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,7 +553,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -532,9 +564,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B4" s="5"/>
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
@@ -577,7 +607,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -588,9 +618,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B12" s="5"/>
       <c r="C12" s="1" t="s">
         <v>4</v>
       </c>
@@ -633,7 +661,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -644,9 +672,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B20" s="5"/>
       <c r="C20" s="1" t="s">
         <v>13</v>
       </c>
@@ -689,7 +715,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -700,9 +726,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B27" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B27" s="5"/>
       <c r="C27" s="1" t="s">
         <v>13</v>
       </c>
@@ -745,7 +769,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -756,9 +780,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B35" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="B35" s="5"/>
       <c r="C35" s="1" t="s">
         <v>16</v>
       </c>
@@ -821,6 +843,13 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B34:B35"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>